--- a/panel/内線設定シート.xlsx
+++ b/panel/内線設定シート.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsq\Documents\asterisk\ABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{491EA197-D448-4ECB-8C11-42EDBCFE41B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1616267D-2BEF-44EC-9292-13041F798CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5820" yWindow="495" windowWidth="22395" windowHeight="14985" xr2:uid="{7AF40BD9-B154-4585-83F9-F2CAA8A99FC8}"/>
+    <workbookView xWindow="5640" yWindow="0" windowWidth="22395" windowHeight="14985" xr2:uid="{7AF40BD9-B154-4585-83F9-F2CAA8A99FC8}"/>
   </bookViews>
   <sheets>
     <sheet name="説明" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>説明</t>
     <rPh sb="0" eb="2">
@@ -301,6 +301,44 @@
     <t>シートはUTF-8で保存してください。</t>
     <rPh sb="10" eb="12">
       <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電話番号</t>
+    <rPh sb="0" eb="2">
+      <t>デンワ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>発信時に使用するCID。ただし発信経路上で後の方が優先される。</t>
+    <rPh sb="0" eb="3">
+      <t>ハッシンジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハッシン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ケイロ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ユウセン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -686,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD513D9-1998-4EAB-83AB-B214D61A534A}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -750,33 +788,44 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>18</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
         <v>22</v>
       </c>
     </row>
